--- a/02_加值成品/生物/生物4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-3 恆定性　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物4-3 恆定性　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>維持體內環境穩定的能力是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>胰島素等</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>尿</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>負回饋</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>恆定性</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>人體體溫大約維持在？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>負回饋</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>把偏離值拉回</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>37℃</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>穩定環境使酵素與代謝正常</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>太熱時身體會？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>收縮減少散熱</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>流汗散熱</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>胰島素</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>降溫</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>太冷時身體會？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>發抖產熱</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>腎臟</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>擴張加速散熱</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>疾病</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>保溫</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>調節血糖的激素？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>胰島素等</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>負回饋</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>胰島素</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>血糖</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>調節水分的器官？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>汗蒸發帶走熱</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>腎臟</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>恆定性</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>升高血糖</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>水分</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>偏離正常即拉回的機制是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>胰島素等</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>擴張加速散熱</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>負回饋</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>恆定性</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>回饋</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>恆定由神經與什麼協調？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>恆定性</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>升高血糖</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>內分泌</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>發抖產熱</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>兩系統</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>血糖過低時身體會？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>升高血糖</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>把偏離值拉回</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>擴張加速散熱</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>負回饋</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>血糖</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>排汗與排尿都幫助調節？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>散熱不及體溫失控上升</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>過熱啟動散熱過冷啟動產熱使體溫回到正常</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>負回饋拉回穩定、正回饋放大變化</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>體內水分或體溫</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-3 恆定性　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物4-3 恆定性　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>流汗如何幫助降溫？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>汗蒸發帶走熱</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>胰島素等</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>升高血糖</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>流汗散熱</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>蒸發</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>天冷血管會？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>腎臟</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>疾病</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>恆定性</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>收縮減少散熱</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>保溫</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>天熱血管會？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>恆定性</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>腎臟</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>發抖產熱</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>擴張加速散熱</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>散熱</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>血糖過高由什麼降低？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>內分泌</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>發抖產熱</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>水分與電解質</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>胰島素</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>降糖</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>恆定是完全不變嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>否,在範圍內波動</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>高時胰島素降低低時升糖素升高</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>負回饋拉回穩定、正回饋放大變化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>流汗散熱降溫發抖產熱保溫</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>範圍</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>負回饋的作用是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>胰島素等</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>胰島素</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>把偏離值拉回</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>水分與電解質</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>水分過多由腎排出成？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>尿</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>疾病</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>相對穩定</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>發抖產熱</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>排水</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>恆定失調可能造成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>恆定性</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>水分與電解質</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>流汗散熱</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>疾病</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>失衡</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>運動後大量流汗需補充？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>水分與電解質</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>發抖產熱</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>收縮減少散熱</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>把偏離值拉回</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>補充</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>恆定讓體內維持在什麼狀態？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>相對穩定</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>擴張加速散熱</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>升高血糖</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>把偏離值拉回</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>穩定</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-3 恆定性　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物4-3 恆定性　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>以體溫為例說明負回饋如何運作？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>散熱不及體溫失控上升</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>過熱啟動散熱過冷啟動產熱使體溫回到正常</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>否,在範圍內波動</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>神經快速反應內分泌持續調節</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>回饋</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何恆定對細胞運作很重要？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>穩定環境使酵素與代謝正常</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>流汗散熱降溫發抖產熱保溫</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>散熱不及體溫過高失恆</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>體內水分或體溫</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>重要</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>說明血糖恆定的雙向調節？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>否,在範圍內波動</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>負回饋拉回穩定、正回饋放大變化</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>穩定環境使酵素與代謝正常</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>高時胰島素降低低時升糖素升高</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>雙向</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>流汗與發抖如何分別調節體溫？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>穩定環境使酵素與代謝正常</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>負回饋拉回穩定、正回饋放大變化</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>流汗散熱降溫發抖產熱保溫</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>散熱不及體溫失控上升</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>神經與內分泌如何協同維持恆定？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>否,在範圍內波動</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>穩定環境使酵素與代謝正常</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>神經快速反應內分泌持續調節</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>流汗散熱降溫發抖產熱保溫</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>協同</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>恆定失衡如中暑的成因？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>負回饋拉回穩定、正回饋放大變化</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>神經快速反應內分泌持續調節</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>過熱啟動散熱過冷啟動產熱使體溫回到正常</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>散熱不及體溫過高失恆</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>失恆</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>腎臟在水分恆定的角色？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>高時胰島素降低低時升糖素升高</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>調節排水量維持水平衡</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>流汗散熱降溫發抖產熱保溫</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>穩定環境使酵素與代謝正常</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>腎</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>負回饋與正回饋的差別(概念)？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>負回饋拉回穩定、正回饋放大變化</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>神經快速反應內分泌持續調節</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>流汗散熱降溫發抖產熱保溫</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>體內水分或體溫</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>發燒是否為體溫恆定失衡？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>胰島素等</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>相對穩定</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>疾病</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>免疫致升溫</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何長時間曝曬易中暑？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>負回饋拉回穩定、正回饋放大變化</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>散熱不及體溫失控上升</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>否,在範圍內波動</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>散熱不及體溫過高失恆</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>失恆</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：生物體能讓體內的溫度、血糖等維持在一定範圍，這種能力叫做恆定性</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>恆定體溫：人體靠恆定性機制，把體溫穩定維持在攝氏37度左右</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>降溫</t>
+          <t>流汗降溫：天氣太熱時身體會流汗，汗水蒸發帶走熱量幫助散熱</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>保溫</t>
+          <t>發抖產熱：天氣太冷時肌肉會不自主發抖，藉由收縮產生熱量來保暖</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>血糖</t>
+          <t>激素調節：胰島素等激素能幫助身體把血糖濃度控制在正常範圍內</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>水分</t>
+          <t>腎臟排水：腎臟能過濾血液調節水分多寡，維持體內水分平衡</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>回饋</t>
+          <t>負回饋機制：當數值偏離正常範圍時，身體會啟動反應把它拉回正常值</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>兩系統</t>
+          <t>兩系統合作：恆定性是靠神經系統和內分泌系統一起協調運作才能維持</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>血糖</t>
+          <t>血糖：身體偵測到血糖過低時，會分泌激素促使血糖濃度回升，維持在正常範圍</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：排汗有助於散熱調節體溫，排尿則能排出多餘水分與代謝廢物，兩者都是身體維持恆定的重要方式</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>蒸發</t>
+          <t>汗水蒸發：汗水在皮膚表面蒸發時會帶走身體的熱量，讓體溫下降</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>保溫</t>
+          <t>血管收縮：天氣寒冷時皮膚血管會收縮，減少血液流到體表以減少散熱</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>散熱</t>
+          <t>血管擴張：天氣炎熱時皮膚血管會擴張，讓更多血液流到體表加速散熱</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>降糖</t>
+          <t>胰島素降糖：血糖濃度過高時，胰島素會被分泌出來幫助降低血糖</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>範圍</t>
+          <t>範圍內波動：恆定並不是數值完全不變，而是維持在一個正常範圍內小幅波動</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>拉回正常：負回饋的作用是偵測到數值偏離後，啟動反應把它調回正常值</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>排水</t>
+          <t>形成尿液：體內水分太多時，腎臟會把多餘的水分過濾出來形成尿液排出</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>失衡</t>
+          <t>失衡致病：若身體的恆定機制失調、無法維持穩定，就可能導致疾病發生</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>補充</t>
+          <t>補充：大量流汗會使體內水分和電解質（如鈉、鉀）流失，運動後應適量補充水分和電解質，避免身體失衡</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：恆定作用能讓體內的溫度、血糖、水分等維持在一個相對穩定的範圍，不會隨外界劇烈變動</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>回饋</t>
+          <t>雙向調節：體溫太高時啟動流汗散熱、太低時啟動發抖產熱，兩種反應都是把體溫拉回正常</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>穩定環境：細胞內的酵素要在穩定的溫度與濃度下才能正常運作，恆定能提供這樣的環境</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>雙向</t>
+          <t>雙向調節：血糖過高時胰島素讓它降低，血糖過低時升糖素讓它升高，維持在正常範圍</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>兩種對策：流汗靠水分蒸發把熱帶走達到降溫，發抖靠肌肉收縮產生熱量達到保溫</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>協同</t>
+          <t>分工合作：神經系統負責快速應變，內分泌系統則負責比較持久緩慢的調節，兩者互相配合</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>失恆</t>
+          <t>散熱不及：當環境太熱、身體來不及散熱，體溫持續升高超出正常範圍，就會造成中暑</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>腎</t>
+          <t>調節排水：腎臟會依照體內水分多寡調整排尿量，藉此維持體內水分的平衡</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>觀念釐清：負回饋是把偏離的數值拉回穩定範圍，正回饋則是讓變化持續放大加劇</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>免疫致升溫</t>
+          <t>免疫致升溫：發燒其實是身體對抗病原體時，主動把體溫調節的基準點暫時調高，屬於體溫恆定機制被重新設定，並非完全失控</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>失恆</t>
+          <t>失恆：長時間曝曬在高溫環境下，身體散熱的速度跟不上吸收熱量的速度，體溫調節機制失去平衡，體溫持續上升就可能中暑</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-3_三種難度測驗卷.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>負回饋</t>
+          <t>發抖產熱</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>把偏離值拉回</t>
+          <t>恆定性</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>穩定環境使酵素與代謝正常</t>
+          <t>胰島素等</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>升高血糖</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>負回饋</t>
+          <t>流汗散熱</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>胰島素</t>
+          <t>疾病</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>內分泌</t>
+          <t>相對穩定</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>發抖產熱</t>
+          <t>恆定性</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>水分與電解質</t>
+          <t>腎臟</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
